--- a/sheets/조재수대금교본/검수/황성옛터.xlsx
+++ b/sheets/조재수대금교본/검수/황성옛터.xlsx
@@ -2882,19 +2882,11 @@
     </row>
     <row r="4" ht="86.26" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B4" s="21"/>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
@@ -3030,7 +3022,7 @@
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -3047,56 +3039,41 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹
-‹</t>
+          <t xml:space="preserve">浹</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹
-‹</t>
+          <t xml:space="preserve">浹</t>
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⊏
-‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -3167,7 +3144,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -3251,11 +3228,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
@@ -3280,46 +3253,21 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/황성옛터.xlsx
+++ b/sheets/조재수대금교본/검수/황성옛터.xlsx
@@ -2882,11 +2882,19 @@
     </row>
     <row r="4" ht="86.26" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
@@ -3022,7 +3030,7 @@
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -3069,7 +3077,11 @@
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⊏</t>
+        </is>
+      </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
@@ -3144,7 +3156,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -3228,7 +3240,11 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>

--- a/sheets/조재수대금교본/검수/황성옛터.xlsx
+++ b/sheets/조재수대금교본/검수/황성옛터.xlsx
@@ -2785,28 +2785,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3165,7 +3165,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3259,7 +3259,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3292,6 +3292,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>